--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -2120,7 +2120,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>AZUL, BEIZ, LILA, NEGRO, ROSADO, BLANCO HUESO, BLANCO, ROJO</t>
+          <t>AZUL, LILA, NEGRO, ROSADO, BLANCO HUESO, BLANCO</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="P26" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>VAQUITA MORADA, AVOCADO FUCSIA, STICH MORADO, KOALA, OSO LOTSO, MINNIE, CERDITO FUCSIA, CAPIBARA CAFE, VAQUITA NEGRA, MICKEY NEGRO, AVOCADO, BEARS</t>
+          <t>STICH MORADO, KOALA, OSO LOTSO, MINNIE, CAPIBARA CAFE, VAQUITA NEGRA, MICKEY NEGRO, AVOCADO, BEARS</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -2766,11 +2766,11 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/qqwsrxvr1ic_1789406839500.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/dvn5kd4fejc_1789406841873.webp</t>
         </is>
       </c>
       <c r="P36" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>SANTA, SANTA CARICATURAS, SANTA TRINEO</t>
+          <t>SANTA, SANTA TRINEO</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="P37" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>VAQUITA ROSA, PANTERA ROSA, SNOOPY FLOR, VAQUITA MOÑO, WINE POOH, ELMO, DONALD, GARFIELD, ELEFANTE, PUCCA, GATICA, OSA MOÑO, OSO, CUTR PUPPY, GATICA MOÑO, CUTE SWAN, CERDITO, PIOLIN</t>
+          <t>VAQUITA ROSA, PANTERA ROSA, SNOOPY FLOR, VAQUITA MOÑO, WINE POOH, ELMO, DONALD, GARFIELD, ELEFANTE, PUCCA, GATICA, OSA MOÑO, OSO, CUTR PUPPY, GATICA MOÑO, CUTE SWAN, CERDITO</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="P38" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>KITTY, CAPIBARA, LABUBU, Oso lottso, PANTERA ROSA, SNOOPY, CAPIBARA CAFE, JIRAFA TIERNA, HELLO KITTY, PATO DONALD</t>
+          <t>KITTY, CAPIBARA, LABUBU, Oso lottso, PANTERA ROSA, SNOOPY, CAPIBARA CAFE, JIRAFA TIERNA, PATO DONALD</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
         </is>
       </c>
       <c r="P55" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>CAPIBARA, VAQUITA MOO, DEISY, MAFALDA MORADO, OSO CARIÑOSO, MINNIE, HELLO KITTY</t>
+          <t>CAPIBARA, VAQUITA MOO, DEISY, MAFALDA MORADO, OSO CARIÑOSO, MINNIE</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4132,7 +4132,7 @@
         </is>
       </c>
       <c r="P57" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>OJOS, MINNIE, HELLO KITTY, OSO PANDA, STICH</t>
+          <t>OJOS, MINNIE, OSO PANDA, STICH</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -4632,7 +4632,7 @@
         </is>
       </c>
       <c r="P65" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>1003145115, RULERGS, OSO ANTIFAZ, COFFE, PRINCESA MARIO, DINO BEAR, GATO FRESA</t>
+          <t>PRINCESA MARIO, DINO BEAR, GATO FRESA</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -4888,11 +4888,11 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/q027f72zlv8_1784914996896.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/aeirxq4xmf_1789406213691.webp</t>
         </is>
       </c>
       <c r="P69" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>OSO LOTSO, POCHACO, CAPIBARA NARANJA, CINAMORROL, BURBUJA, 1002416596</t>
+          <t>POCHACO, CAPIBARA NARANJA, CINAMORROL, BURBUJA, 1002416596</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -5470,11 +5470,11 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/e0wxiek6bya_1784951657522.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/1pwd5aw4xvn_1784951658664.jpg</t>
         </is>
       </c>
       <c r="P78" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>HELLO KITTY, OSO LOTSO, MICKEY, PIOLIN, TIGERS, PINGUINOS, AVOCADO, CERDITO, CAPIBARA, BAMBI, PALETA LILA, BOB ESPONJA, CINAMORROL, MINNI FLOR, ELEFANTE, AVOCADO FUCSIA, BOB BONNY, STICH, CUTE, OSO PANDA, MAFALDA, PIOLIN AMARILLO, OVEJA NUVE, MY MELODDY, OSA</t>
+          <t>OSO LOTSO, MICKEY, HELLO KITTY, TIGERS, PINGUINOS, AVOCADO, CERDITO, CAPIBARA, BAMBI, PALETA LILA, BOB ESPONJA, CINAMORROL, MINNI FLOR, ELEFANTE, STICH, OSO PANDA, MAFALDA, OVEJA NUVE, MY MELODDY</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -6276,11 +6276,11 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/wq6vkaejj3f_1784922917937.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/jxcws9687y_1784922919118.jpg</t>
         </is>
       </c>
       <c r="P91" s="2" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="92">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-23 18:24</t>
+          <t>2026-10-24 00:29</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -5691,10 +5691,10 @@
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>3</v>
+        <v>36000</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>2</v>
+        <v>26000</v>
       </c>
       <c r="I82" s="3" t="n">
         <v>1</v>
@@ -5749,7 +5749,7 @@
       <c r="E83" s="2" t="inlineStr"/>
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="3" t="n">
-        <v>3</v>
+        <v>36000</v>
       </c>
       <c r="H83" s="3" t="n"/>
       <c r="I83" s="3" t="n"/>
@@ -5803,10 +5803,10 @@
       <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="3" t="n">
-        <v>3</v>
+        <v>36000</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>2</v>
+        <v>26000</v>
       </c>
       <c r="I84" s="3" t="n">
         <v>1</v>
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-24 00:29</t>
+          <t>2026-10-24 06:23</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-24 06:23</t>
+          <t>2026-10-24 12:22</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-24 12:22</t>
+          <t>2026-10-24 18:18</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-24 18:18</t>
+          <t>2026-10-25 00:21</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25 00:21</t>
+          <t>2026-10-25 06:24</t>
         </is>
       </c>
     </row>
